--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T09:37:24+00:00</t>
+    <t>2026-01-28T12:34:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T12:34:00+00:00</t>
+    <t>2026-01-30T08:45:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:50:43+00:00</t>
+    <t>2026-03-18T15:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:56:08+00:00</t>
+    <t>2026-04-09T09:35:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:35:35+00:00</t>
+    <t>2026-04-09T10:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T10:04:08+00:00</t>
+    <t>2026-04-09T11:10:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:10:35+00:00</t>
+    <t>2026-04-09T11:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-main/StructureDefinition-at-messaging-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T11:58:42+00:00</t>
+    <t>2026-05-06T12:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
